--- a/Phase2_Classifications.xlsx
+++ b/Phase2_Classifications.xlsx
@@ -418,7 +418,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="217" customWidth="1" min="3" max="3"/>
+    <col width="197" customWidth="1" min="3" max="3"/>
     <col width="83" customWidth="1" min="4" max="4"/>
     <col width="83" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -467,21 +467,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A Performance Benchmark of Open-Source Network Monitoring Systems</t>
+          <t>A Qualitative Analysis of the German Road Traffic Regulations (StVO) for Automated Driving</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+          <t>Sec M / Div 69 - Legal and accounting activities</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -495,21 +495,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A Performance Benchmark of Open-Source Network Monitoring Systems</t>
+          <t>ARTigo: Social Image Tagging (Aggregated Data)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -523,17 +523,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A Qualitative Analysis of the German Road Traffic Regulations (StVO) for Automated Driving</t>
+          <t>ARTigo: Social Image Tagging (Aggregated Data)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sec M / Div 69 - Legal and accounting activities</t>
+          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -551,17 +551,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Banco de Dados QDA - CPI Covid-19</t>
+          <t>ARTigo: Social Image Tagging (Aggregated Data)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
+        </is>
+      </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -575,17 +579,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Data, Code, and Materials for "Evaluating AI-Generated Counseling Dialogues With Synthetic Clients: A Response-Rendering Audit in Japanese Motivational Interviewing Simulations"</t>
+          <t>ARTigo: Social Image Tagging (Raw Data)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -603,15 +607,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dataset "Inverse Theoretical Spectroscopy via Monte-Carlo Sampling — From Spectra to Ensembles of Molecular Structures"</t>
+          <t>ARTigo: Social Image Tagging (Raw Data)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
+        </is>
+      </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
@@ -627,17 +635,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dataset on observed practices in the provision of patient-centered primary care in rural Eastern Uganda.</t>
+          <t>ARTigo: Social Image Tagging (Raw Data)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sec A / Div 01 - Crop and animal production, hunting and related service activities</t>
+          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -655,19 +663,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dataset on observed practices in the provision of patient-centered primary care in rural Eastern Uganda.</t>
+          <t>AfD Discourse Corpus (2013–2026): A Multi-Arena Corpus for Critical Discourse Analysis</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Sec A / Div 01 - Crop and animal production, hunting and related service activities</t>
-        </is>
-      </c>
+          <t>Sec F / Div 41 - Construction of buildings</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>1</v>
       </c>
@@ -683,19 +687,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dataset on observed practices in the provision of patient-centered primary care in rural Eastern Uganda.</t>
+          <t>Banco de Dados QDA - CPI Covid-19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Sec A / Div 01 - Crop and animal production, hunting and related service activities</t>
-        </is>
-      </c>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
         <v>1</v>
       </c>
@@ -711,21 +711,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Do Geospatial Foundation Models Outperform Sentinel-2 Composites? A Counterexample from Semantic Segmentation of Tea Plantations in Western Kenya</t>
+          <t>CascadeMAP dataset of Design-of-Experiment optimization of glycerol detection pathway using fluorescence detection</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
-        </is>
-      </c>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -739,12 +735,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EMGLAB downsample analysis data</t>
+          <t>Data for the Manuscript with the Title: Structural and functional basis of antinociceptive action of χ-conotoxin AoIA at the noradrenaline transporter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
+          <t>Sec R / Div 93 - Sports activities and amusement and recreation activities</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -763,15 +759,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Effects of Data Resolution on the Analysis of Planetary Compressional Structures</t>
+          <t>Dataset from: Healthcare professionals' experiences of encounters with family members exposed to violence perpetrated by patients with brain tumors: a qualitative study</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sec Q / Div 86 - Human health activities</t>
+        </is>
+      </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
@@ -787,15 +787,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>F2AF Metadata-Hiding F2FS Corpus</t>
+          <t>Dataset from: Healthcare professionals' experiences of encounters with family members exposed to violence perpetrated by patients with brain tumors: a qualitative study</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sec Q / Div 86 - Human health activities</t>
+        </is>
+      </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
@@ -811,21 +815,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GaitMoText: A Multimodal Dataset for Clinical Gait Analysis compromising Optical Motion Capture and Textual Gait Analyses from Patients undergoing Total Knee Arthroplasty</t>
+          <t>Dataset from: Healthcare professionals' experiences of encounters with family members exposed to violence perpetrated by patients with brain tumors: a qualitative study</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>Sec Q / Div 86 - Human health activities</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
-        </is>
-      </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -839,21 +843,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GaitMoText: A Multimodal Dataset for Clinical Gait Analysis compromising Optical Motion Capture and Textual Gait Analyses from Patients undergoing Total Knee Arthroplasty</t>
+          <t>Dataset to reproduce the figures of "Opposing entrainment effects of cloud droplet sedimentation during the pre-breakup stage of the stratocumulus to cumulus transition"</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
-        </is>
-      </c>
+          <t>Sec J / Div 63 - Information service activities</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -867,21 +867,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GaitMoText: A Multimodal Dataset for Clinical Gait Analysis compromising Optical Motion Capture and Textual Gait Analyses from Patients undergoing Total Knee Arthroplasty</t>
+          <t>Datasets for Tutorials on InSAR Time Series Analysis with SARvey and InSAR Explorer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
-        </is>
-      </c>
+          <t>Sec J / Div 63 - Information service activities</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -895,19 +891,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>InterGenSynchrony Dataset</t>
+          <t>Dynamic Surface Tension Database of Surfactants (DST‑SurfDB)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
-        </is>
-      </c>
+          <t>Sec J / Div 58 - Publishing activities</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>1</v>
       </c>
@@ -923,7 +915,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Johnson Pandemic Corpus 2020 (JPanC20)</t>
+          <t>Emergency design data</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -931,11 +923,7 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
         <v>1</v>
       </c>
@@ -951,7 +939,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Life-cycle trajectory inference links temperature-gated progenitors to reproductive fate: supporting data and code</t>
+          <t>Fast Breakdowns Observed in the Initial Leaders of Two Energetic Compact Strokes</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -961,7 +949,7 @@
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -975,17 +963,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Meta-analysis of GWAS on apolipoprotein A-IV</t>
+          <t>From Failure to Persistence: A Lifecycle Study of Reliability in Stack Overflow Answers – Replication Package</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -999,12 +987,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pocillopora and Cladocopium gene expression levels and Cladocopium SNPs</t>
+          <t>From Failure to Persistence: A Lifecycle Study of Reliability in Stack Overflow Answers – Replication Package</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1023,7 +1011,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Qualitative transcripts on eco-innovation, sustainability and circular economy in the Spanish olive oil sector</t>
+          <t>Johnson Pandemic Corpus 2020 (JPanC20)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1033,7 +1021,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
+          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1051,19 +1039,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qualitative transcripts on eco-innovation, sustainability and circular economy in the Spanish olive oil sector</t>
+          <t>Kuesioner Penelitian Pengaruh Bullying terhadap Kepercayaan Diri Siswa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
-        </is>
-      </c>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
         <v>1</v>
       </c>
@@ -1079,17 +1063,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote Sensing Data Udhruh Roman fortress, Jordan</t>
+          <t>Oncodrive3D datasets</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sec F / Div 41 - Construction of buildings</t>
+        </is>
+      </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1103,21 +1091,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Reproducibility data for "Where and When Surface Soil Moisture Can Explain Operational Drought": GM-LSTM station predictions, SPI baselines, and USDM labels</t>
+          <t>Plumbom et al. 2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Sec J / Div 63 - Information service activities</t>
-        </is>
-      </c>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1131,12 +1115,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Reproducibility data for "Where and When Surface Soil Moisture Can Explain Operational Drought": GM-LSTM station predictions, SPI baselines, and USDM labels</t>
+          <t>Proteomic and transcriptomic datasets of the desert cyanobacterium Gloeocapsopsis dulcis under long-term desiccation stress</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1145,7 +1129,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1159,21 +1143,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scenario variations of the European energy system driven by level of landscape impact scenicness preservation</t>
+          <t>Qualitative Oral History Interview Transcripts on European Contemporary Dance Heritage</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sec M / Div 69 - Legal and accounting activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1187,15 +1171,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Student AI Disclosure and Faculty Estimation Gaps in Arabic-Medium Higher Education Assessment</t>
+          <t>Qualitative Oral History Interview Transcripts on European Contemporary Dance Heritage</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
+        </is>
+      </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
@@ -1211,15 +1199,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Student AI Disclosure and Faculty Estimation Gaps in Arabic-Medium Higher Education Assessment</t>
+          <t>Qualitative Oral History Interview Transcripts on European Contemporary Dance Heritage</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
+        </is>
+      </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
@@ -1235,7 +1227,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Student AI Disclosure and Faculty Estimation Gaps in Arabic-Medium Higher Education Assessment</t>
+          <t>ToxKAN-Dataset</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1243,7 +1235,11 @@
           <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sec Q / Div 86 - Human health activities</t>
+        </is>
+      </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
@@ -1259,15 +1255,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[FLUTE] Prostate Cancer Use Case</t>
+          <t>Transcriptional co-expression and sequence-model scoring of the Prochlorococcus MED4 CrY2H-seq interactome: a 227-run RNA-seq analysis with functional, WGCNA, and model-based cross-checks</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
+        </is>
+      </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
@@ -1283,15 +1283,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[FLUTE] Prostate Cancer Use Case</t>
+          <t>Transcriptional co-expression and sequence-model scoring of the Prochlorococcus MED4 CrY2H-seq interactome: a 227-run RNA-seq analysis with functional, WGCNA, and model-based cross-checks</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
+        </is>
+      </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
@@ -1307,21 +1311,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[Supplemental Material] Examining Benchmark Quality in Code Generation</t>
+          <t>UVIndoorLoc-BLE-AoA&amp;IQ Dataset</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1330,26 +1334,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QDA_PROJECT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[Supplemental Material] Examining Benchmark Quality in Code Generation</t>
+          <t>Implementation Science, Program Fidelity, and Program Delivery in Scaling Early Literacy Interventions for Children Aged 3–13: A Systematic Review</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
-        </is>
-      </c>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Implementation Science, Program Fidelity, and Program Delivery in Scaling Early Literacy Interventions for Children Aged 3–13: A Systematic Review</t>
+          <t>PLANET4B Business Models Dataset Pisa [UNIPI] 20251014 v2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1371,9 +1371,13 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37">
@@ -1387,7 +1391,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PLANET4B Business Models Dataset Pisa [UNIPI] 20251014 v2</t>
+          <t>PLANET4B Frame Analysis Dataset Pisa [UNIPI] 20251013 v2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1401,7 +1405,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38">
@@ -1415,7 +1419,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PLANET4B Frame Analysis Dataset Pisa [UNIPI] 20251013 v2</t>
+          <t>Polish debates on higher education in the Sejm and party manifestos</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1429,7 +1433,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -1443,7 +1447,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Polish debates on higher education in the Sejm and party manifestos</t>
+          <t>Supporting Data for Scoping Review on Interlanguage Pragmatics in EFL Contexts</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1451,13 +1455,9 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -1466,22 +1466,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>QDA_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Supporting Data for Scoping Review on Interlanguage Pragmatics in EFL Contexts</t>
+          <t>2024-04-08 Partial Solar Eclipse ESID#204</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+        </is>
+      </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -1495,21 +1499,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A refined Saccharomyces cerevisiae reference transcriptome from Direct RNA Sequencing, with a reusable pipeline for UTR annotation updates</t>
+          <t>2024-04-08 Partial Solar Eclipse ESID#204</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sec F / Div 41 - Construction of buildings</t>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -1523,21 +1527,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ALIGHT Survey Dataset (Aggregated and Anonymized Results): Antarctic Living Heritage Survey, 2025</t>
+          <t>2024-04-08 Total Solar Eclipse ESID#292</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -1551,21 +1555,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ALIGHT Survey Dataset (Aggregated and Anonymized Results): Antarctic Living Heritage Survey, 2025</t>
+          <t>2024-04-08 Total Solar Eclipse ESID#294</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
@@ -1579,21 +1583,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AMYPAD PNHS - Integrated dataset (Harmonized and Derived) v202606</t>
+          <t>Aggregated thematic data and research materials: Anti-vegan focus groups in Greece and the Netherlands</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+          <t>Sec J / Div 58 - Publishing activities</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -1607,7 +1611,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Analysis and Design of a Mobile-Based Information System for the Dzikra Application at PT Bejana Inovasi Global</t>
+          <t>Aggregated thematic data and research materials: Anti-vegan focus groups in Greece and the Netherlands</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1615,9 +1619,13 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Sec J / Div 58 - Publishing activities</t>
+        </is>
+      </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -1631,7 +1639,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Analysis and Design of a Mobile-Based Information System for the Dzikra Application at PT Bejana Inovasi Global</t>
+          <t>Aggregated thematic data and research materials: Anti-vegan focus groups in Greece and the Netherlands</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1639,9 +1647,13 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sec J / Div 58 - Publishing activities</t>
+        </is>
+      </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -1703,17 +1715,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ant behaviour in the Anthropocene: A meta-analysis of human-induced environmental change effects on ant behaviour</t>
+          <t>Asynchrony of ageing among traits in a wild bird population</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50">
@@ -1727,17 +1739,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Attendance Reminder Feature: Interview Guide, Coding Scheme, and Thematic Analysis</t>
+          <t>Bridging Sensory Science and Economic Value</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1751,17 +1763,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Attendance Reminder Feature: Interview Guide, Coding Scheme, and Thematic Analysis</t>
+          <t>CARDIOMED Registry — Anonymised Dataset: Haematocrit and in-hospital mortality in ADHF at 2,600 m a.s.l.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Sec Q / Div 86 - Human health activities</t>
+        </is>
+      </c>
       <c r="F51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -1775,15 +1791,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avibase-based bird checklist datasets for Shirvan National Park and Gizilaghaj regional proxy areas</t>
+          <t>CARDIOMED Registry — Anonymised Dataset: Haematocrit and in-hospital mortality in ADHF at 2,600 m a.s.l.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sec R / Div 93 - Sports activities and amusement and recreation activities</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Sec Q / Div 86 - Human health activities</t>
+        </is>
+      </c>
       <c r="F52" t="n">
         <v>3</v>
       </c>
@@ -1799,17 +1819,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bacteria samples BRB</t>
+          <t>DEVELOPING LINGUODISCURSIVE COMPETENCE IN THE DIGITAL TOURISM ENVIRONMENT: LINGUOPRAGMATIC FEATURES OF ONLINE PLATFORMS AND MULTIMODAL COMMUNICATION</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+        </is>
+      </c>
       <c r="F53" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1823,17 +1847,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bacteria samples BRB</t>
+          <t>DEVELOPING LINGUODISCURSIVE COMPETENCE IN THE DIGITAL TOURISM ENVIRONMENT: LINGUOPRAGMATIC FEATURES OF ONLINE PLATFORMS AND MULTIMODAL COMMUNICATION</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+        </is>
+      </c>
       <c r="F54" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1847,15 +1875,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bridging Sensory Science and Economic Value</t>
+          <t>DIGITAL TRANSFORMATION AND AI-DRIVEN SUPPLY CHAIN IMPROVEMENT IN THE INDONESIAN AGROCHEMICAL INDUSTRY</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Sec M / Div 69 - Legal and accounting activities</t>
+        </is>
+      </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
@@ -1871,21 +1903,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Characterizing Participants of Community Question-Answering Sites: A Study of Stack Exchange Project Management - Supplementary Material</t>
+          <t>DIGITAL TRANSFORMATION AND AI-DRIVEN SUPPLY CHAIN IMPROVEMENT IN THE INDONESIAN AGROCHEMICAL INDUSTRY</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+          <t>Sec M / Div 69 - Legal and accounting activities</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1899,21 +1931,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Characterizing Participants of Community Question-Answering Sites: A Study of Stack Exchange Project Management - Supplementary Material</t>
+          <t>DIGITAL TRANSFORMATION AND AI-DRIVEN SUPPLY CHAIN IMPROVEMENT IN THE INDONESIAN AGROCHEMICAL INDUSTRY</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+          <t>Sec M / Div 69 - Legal and accounting activities</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1927,21 +1959,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Characterizing Participants of Community Question-Answering Sites: A Study of Stack Exchange Project Management - Supplementary Material</t>
+          <t>Data and Scripts for: Techno-Economic Analysis of Hydrocarbon-CO2 Binary Mixtures in Heat Pump-Based Thermal Energy Storages</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec J / Div 58 - Publishing activities</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -1955,21 +1987,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Companion Datasets: Driving Healthy and Sustainable Mobility: Emotional and Cognitive Pathways from Message Framing to the Effectiveness of Car-Advertising Warnings</t>
+          <t>Data and Scripts for: Techno-Economic Analysis of Hydrocarbon-CO2 Binary Mixtures in Heat Pump-Based Thermal Energy Storages</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
+          <t>Sec J / Div 58 - Publishing activities</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -1983,21 +2015,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Curated datasets for plant single cell RNA-sequencing studies containing root tissue</t>
+          <t>Data for "Predominant proton insertion during electrochemical cycling of ε-VOPO4 in a non-aqueous Ca ion electrolyte"</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
           <t>Sec J / Div 58 - Publishing activities</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
@@ -2011,7 +2039,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Curated datasets for plant single cell RNA-sequencing studies containing root tissue</t>
+          <t>Data for: "The limited communication of corrections to users of scholarly platforms"</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2019,13 +2047,9 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -2039,7 +2063,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DEVELOPING LINGUODISCURSIVE COMPETENCE IN THE DIGITAL TOURISM ENVIRONMENT: LINGUOPRAGMATIC FEATURES OF ONLINE PLATFORMS AND MULTIMODAL COMMUNICATION</t>
+          <t>Data from: Fitness change in relation to mutation number in spontaneous mutation accumulation lines of Chlamydomonas reinhardtii</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2047,13 +2071,9 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -2067,21 +2087,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DEVELOPING LINGUODISCURSIVE COMPETENCE IN THE DIGITAL TOURISM ENVIRONMENT: LINGUOPRAGMATIC FEATURES OF ONLINE PLATFORMS AND MULTIMODAL COMMUNICATION</t>
+          <t>Data set Non-volatile metabolite profiling integrated with QDA sensory evaluation of white tea</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -2095,7 +2111,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DEVELOPING LINGUODISCURSIVE COMPETENCE IN THE DIGITAL TOURISM ENVIRONMENT: LINGUOPRAGMATIC FEATURES OF ONLINE PLATFORMS AND MULTIMODAL COMMUNICATION</t>
+          <t>Data, analysis codes, analysis output and survey questionnaire for: Integrating Threatened Biodiversity in Monetary Ecosystem Accounting: Choice Experiments and Simulated Exchange Values</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2105,11 +2121,11 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+          <t>Sec J / Div 63 - Information service activities</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -2123,7 +2139,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Data from: Fitness change in relation to mutation number in spontaneous mutation accumulation lines of Chlamydomonas reinhardtii</t>
+          <t>Data, analysis codes, analysis output and survey questionnaire for: Integrating Threatened Biodiversity in Monetary Ecosystem Accounting: Choice Experiments and Simulated Exchange Values</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2131,9 +2147,13 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Sec J / Div 63 - Information service activities</t>
+        </is>
+      </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -2147,17 +2167,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Data set Non-volatile metabolite profiling integrated with QDA sensory evaluation of white tea</t>
+          <t>Dataset for Realization of QDA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+          <t>Sec R / Div 90 - Creative, arts and entertainment activities</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67">
@@ -2171,17 +2191,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dataset for Realization of QDA</t>
+          <t>Dataset for Teleconnection-Based Modeling of Extreme Precipitation in South America Using Climate Indices</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sec R / Div 90 - Creative, arts and entertainment activities</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+        </is>
+      </c>
       <c r="F67" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68">
@@ -2195,17 +2219,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dataset for the Paper: When Passing Tests Hides Vulnerabilities: An Empirical Study of Silent Failures in Agentic Systems</t>
+          <t>Dataset for Teleconnection-Based Modeling of Extreme Precipitation in South America Using Climate Indices</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+        </is>
+      </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69">
@@ -2219,17 +2247,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dataset for the Paper: When Passing Tests Hides Vulnerabilities: An Empirical Study of Silent Failures in Agentic Systems</t>
+          <t>Dataset: Chicago Atlantic Real Estate Finance, Inc. (REFI) Stock Performance</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
+          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Sec R / Div 90 - Creative, arts and entertainment activities</t>
+        </is>
+      </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -2243,7 +2275,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dataset for: Social Media, Environmental Knowledge, and Student Green Behavior: The Role of Environmental Concern</t>
+          <t>Datensatz der Expert:inneninterviews im Projekt RPSKM / Dataset of the expert interviews in the project RPCSA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2251,13 +2283,9 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71">
@@ -2271,15 +2299,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dataset of Chemical Engineering Curricula and Course Syllabi from Brazilian and U.S. Universities</t>
+          <t>Ecological Political Economy: a critical realist approach to ecological economics and political ecology</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+          <t>Sec J / Div 58 - Publishing activities</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
+        </is>
+      </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
@@ -2295,15 +2327,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dataset of Chemical Engineering Curricula and Course Syllabi from Brazilian and U.S. Universities</t>
+          <t>Ecological Political Economy: a critical realist approach to ecological economics and political ecology</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+          <t>Sec J / Div 58 - Publishing activities</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
+        </is>
+      </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
@@ -2319,17 +2355,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dataset on the solvent screening and extraction optimization of volatile compounds from Sequoia sempervirens leaves</t>
+          <t>Ecological Political Economy: a critical realist approach to ecological economics and political ecology</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
+          <t>Sec J / Div 58 - Publishing activities</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2347,21 +2383,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dataset on the solvent screening and extraction optimization of volatile compounds from Sequoia sempervirens leaves</t>
+          <t>Efficient globin production during terminal erythropoiesis depends on the cooperative action of TENT5C poly(A) polymerase and LARP4B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
           <t>Sec J / Div 63 - Information service activities</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75">
@@ -2375,21 +2407,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dataset: Chicago Atlantic Real Estate Finance, Inc. (REFI) Stock Performance</t>
+          <t>Efficient globin production during terminal erythropoiesis depends on the cooperative action of TENT5C poly(A) polymerase and LARP4B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Sec R / Div 90 - Creative, arts and entertainment activities</t>
-        </is>
-      </c>
+          <t>Sec J / Div 63 - Information service activities</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="76">
@@ -2403,7 +2431,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dataset: Structural modifications of grain boundaries due to vacancy segregation</t>
+          <t>Explore Wales: A Geospatial Dataset of Heritage and Visitor Locations</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2411,7 +2439,11 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
       <c r="F76" t="n">
         <v>2</v>
       </c>
@@ -2427,7 +2459,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>From Sustainable to Regenerative Heritage Tourism: The Role of Community Narratives and Interpretation in Enhancing Visitor Experience in the UAE</t>
+          <t>Extracted Data from a Scoping Review of Machine Learning Approaches for Wave Propagation Modeling in Seismology</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2437,11 +2469,11 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sec M / Div 69 - Legal and accounting activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -2455,7 +2487,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>From Sustainable to Regenerative Heritage Tourism: The Role of Community Narratives and Interpretation in Enhancing Visitor Experience in the UAE</t>
+          <t>Extracted Data from a Scoping Review of Machine Learning Approaches for Wave Propagation Modeling in Seismology</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2465,11 +2497,11 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sec M / Div 69 - Legal and accounting activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -2483,17 +2515,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>INTEGRATION OF INTERACTIVE AND PROBLEM-BASED EDUCATIONAL TECHNOLOGIES IN DEVELOPING THE CRITICAL THINKING COMPETENCE OF FUTURE TEACHERS</t>
+          <t>Extracted Data from a Scoping Review of Machine Learning Approaches for Wave Propagation Modeling in Seismology</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2511,21 +2543,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>INTEGRATION OF INTERACTIVE AND PROBLEM-BASED EDUCATIONAL TECHNOLOGIES IN DEVELOPING THE CRITICAL THINKING COMPETENCE OF FUTURE TEACHERS</t>
+          <t>FORGE code, trained models and source data for RNA tertiary-structure information mapping</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81">
@@ -2539,21 +2567,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>INTEGRATION OF INTERACTIVE AND PROBLEM-BASED EDUCATIONAL TECHNOLOGIES IN DEVELOPING THE CRITICAL THINKING COMPETENCE OF FUTURE TEACHERS</t>
+          <t>FORGE code, trained models and source data for RNA tertiary-structure information mapping</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82">
@@ -2567,17 +2591,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indonesia Gender Construction in Vasectomy Discourse in the Era of Digital Transformation (2024–2025)</t>
+          <t>Genomic, CRISPR, and structural datasets underlying Vibrio–phage interaction and defense system analysis</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sec F / Div 41 - Construction of buildings</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83">
@@ -2591,21 +2615,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Interim survey data and instruments: teachers as agents of ecological reflection in Bulgarian philosophy and civic education</t>
+          <t>High-resolution Multi-environmental-indicator Livestock Emissions of China (HMLE-China): A 1-km Stage-resolved Emission Inventory</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec M / Div 69 - Legal and accounting activities</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84">
@@ -2619,7 +2643,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Interim survey data and instruments: teachers as agents of ecological reflection in Bulgarian philosophy and civic education</t>
+          <t>Improved Iso-Seq-based genome annotations for Australian wild rice species O. rufipogon and O. meridionalis</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2627,11 +2651,7 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
         <v>3</v>
       </c>
@@ -2647,7 +2667,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Interim survey data and instruments: teachers as agents of ecological reflection in Bulgarian philosophy and civic education</t>
+          <t>Influence of Structural Disorder on Self-Trapped Exciton Luminescence in Natural Quartz</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2655,13 +2675,9 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86">
@@ -2675,7 +2691,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Interview &amp; Testing Results for Paper "Designing Dark-Pattern-Free User Experience for Investment Applications: A User-Centered Design Approach"</t>
+          <t>Investigating Enablers, Barriers, and Consequences of Psychological Safety in Software Engineering</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2685,7 +2701,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
+          <t>Sec Q / Div 86 - Human health activities</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -2703,7 +2719,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Interview-based comparative assessment of birdwatching ecotourism potential in Shirvan and Gizilaghaj National Parks</t>
+          <t>Master Analytical Dataset: ESP-Content Collaborative Teaching and Longitudinal Student Motivation Frameworks (Vols. 1–7)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2713,11 +2729,11 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88">
@@ -2731,7 +2747,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lipidomics of MKTAL cell line and microdissected TAL</t>
+          <t>Master Analytical Dataset: ESP-Content Collaborative Teaching and Longitudinal Student Motivation Frameworks (Vols. 1–7)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2739,9 +2755,13 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
@@ -2755,21 +2775,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Metrics Data for Quantifying Multidimensional Impacts of Landscape Change in California's Sacramento–San Joaquin Delta</t>
+          <t>Master Analytical Dataset: ESP-Content Collaborative Teaching and Longitudinal Student Motivation Frameworks (Vols. 1–7)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
@@ -2783,21 +2803,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Metrics Data for Quantifying Multidimensional Impacts of Landscape Change in California's Sacramento–San Joaquin Delta</t>
+          <t>Model and code for: Assessing the Cost of CO₂ Avoided for CCS in the Cement Industry: A Comparative Analysis of Denmark and Germany</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
-        </is>
-      </c>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -2811,21 +2827,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Metrics Data for Quantifying Multidimensional Impacts of Landscape Change in California's Sacramento–San Joaquin Delta</t>
+          <t>Model and code for: Assessing the Cost of CO₂ Avoided for CCS in the Cement Industry: A Comparative Analysis of Denmark and Germany</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
-        </is>
-      </c>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -2839,21 +2851,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Process of Process Mining: A Multi-perspective Event Log</t>
+          <t>Music Therapy Today (World Federation of Music Therapy): a bibliometric and content-analysis dataset, 2000–2023</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
+          <t>Sec Q / Div 86 - Human health activities</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
@@ -2867,21 +2879,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Process of Process Mining: A Multi-perspective Event Log</t>
+          <t>Open Science Monitoring Initiatives Dataset v01</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -2895,21 +2907,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Process of Process Mining: A Multi-perspective Event Log</t>
+          <t>Open Science Monitoring Initiatives Dataset v01</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -2923,21 +2935,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Process of Process Mining: A Multi-perspective Event Log</t>
+          <t>Open Science Monitoring Initiatives Dataset v01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -2951,21 +2963,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Public-methodology audit dataset for real-asset sustainability-finance interpretation in emerging-market built environments</t>
+          <t>Physiological adaption of Fusarium commune to oxygen limitation under denitrifying conditions is primarily linked to energy conservation by substrate level phosphorylation</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
@@ -2979,21 +2987,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Questionnaire data on virtual ballet experience</t>
+          <t>Process of Process Mining: A Multi-perspective Event Log</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec J / Div 63 - Information service activities</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sec R / Div 90 - Creative, arts and entertainment activities</t>
+          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98">
@@ -3007,21 +3015,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Questionnaire data on virtual ballet experience</t>
+          <t>Process of Process Mining: A Multi-perspective Event Log</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec J / Div 63 - Information service activities</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sec R / Div 90 - Creative, arts and entertainment activities</t>
+          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
@@ -3035,7 +3043,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Replication Package for "FinTech Adoption, Investor Sentiment, and the Turnover–Return Relation: A Panel Threshold Analysis of Borsa Istanbul"</t>
+          <t>Research Dataset: Schutzian Phenomenological Analysis of Civic Identity Formation in Pesantren Families, West Java</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3045,7 +3053,7 @@
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -3059,21 +3067,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Satellite-derived Shoreline Change in Portugal (1984-2024)</t>
+          <t>Research Dataset: Schutzian Phenomenological Analysis of Civic Identity Formation in Pesantren Families, West Java</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Sec M / Div 69 - Legal and accounting activities</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Sec R / Div 90 - Creative, arts and entertainment activities</t>
-        </is>
-      </c>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
@@ -3087,7 +3091,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Semi-structured interview guide for the study of public perceptions of timber construction in Greater Concepción, Chile</t>
+          <t>Research Dataset: Schutzian Phenomenological Analysis of Civic Identity Formation in Pesantren Families, West Java</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3095,13 +3099,9 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Sec F / Div 41 - Construction of buildings</t>
-        </is>
-      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
@@ -3115,21 +3115,21 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Supplementary Material and Reproducibility Package: The Handover Problem — Governing Autonomy Transitions in Human–AI Collaboration</t>
+          <t>Supplementary Info Package - Developer Task Delegation to LLMs and the Trust Factor: A Mixed Methods Study</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103">
@@ -3143,21 +3143,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Supplementary Material and Reproducibility Package: The Handover Problem — Governing Autonomy Transitions in Human–AI Collaboration</t>
+          <t>Supplementary Info Package - Developer Task Delegation to LLMs and the Trust Factor: A Mixed Methods Study</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104">
@@ -3171,21 +3171,21 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Supporting Data and Regulatory Analysis Tools for the Assessment of Psychedelic Clinical Trials</t>
+          <t>Supplementary Info Package - Developer Task Delegation to LLMs and the Trust Factor: A Mixed Methods Study</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105">
@@ -3199,21 +3199,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Supporting Data and Regulatory Analysis Tools for the Assessment of Psychedelic Clinical Trials</t>
+          <t>Supplymentary Materials for "Who Pays the Review Cost? Triage, Fairness, and Accountability in AI-authored Pull Requests"</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -3227,21 +3227,21 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Supporting Data and Regulatory Analysis Tools for the Assessment of Psychedelic Clinical Trials</t>
+          <t>Supplymentary Materials for "Who Pays the Review Cost? Triage, Fairness, and Accountability in AI-authored Pull Requests"</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Technischer Vergleich von CAQDAS Funktionalitäten in 2026</t>
+          <t>THE ROLE OF THE JOURNEY MOTIF IN THE EVOLUTION OF LITERARY HEROES: A COMPARATIVE STUDY OF ENGLISH AND UZBEK LITERATURE</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Technischer Vergleich von CAQDAS Funktionalitäten in 2026</t>
+          <t>THE ROLE OF THE JOURNEY MOTIF IN THE EVOLUTION OF LITERARY HEROES: A COMPARATIVE STUDY OF ENGLISH AND UZBEK LITERATURE</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Technischer Vergleich von CAQDAS Funktionalitäten in 2026</t>
+          <t>THE ROLE OF THE JOURNEY MOTIF IN THE EVOLUTION OF LITERARY HEROES: A COMPARATIVE STUDY OF ENGLISH AND UZBEK LITERATURE</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>The Impact of Artificial Intelligence Knowledge and Perception on Accounting Students' Career Readiness in the Digital Era</t>
+          <t>Table S1. Frequency table derived from the inductive qualitative analysis.</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3335,13 +3335,9 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3355,7 +3351,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>The circadian rhythm of thermal preference in Atlantic salmon modify the internal affective state (DataSet)</t>
+          <t>Table S1. Frequency table derived from the inductive qualitative analysis.</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3379,7 +3375,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tiny Scratches Belong to Movies: Perception of Digitally Cleaned Films - dataset</t>
+          <t>Technischer Vergleich von CAQDAS Funktionalitäten in 2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3387,13 +3383,9 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3407,21 +3399,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tiny Scratches Belong to Movies: Perception of Digitally Cleaned Films - dataset</t>
+          <t>Thermographic data for manuscript Mus.4189-D-14,8 (SLUB)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114">
@@ -3435,17 +3423,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Vanessa's Data Set</t>
+          <t>Thermographic data for manuscript Mus.4645-D-1 (SLUB)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="115">
@@ -3459,21 +3447,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Zenodo: Interview Instrument and Transcript for Research Entitled Designing an AI-Responsive Early Childhood Curriculum: A Conceptual Framework for Supporting Developmental Learning Trajectories in Preschool Education</t>
+          <t>Thermographic data for manuscript Mus.4657-D-503 (SLUB)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">

--- a/Phase2_Classifications.xlsx
+++ b/Phase2_Classifications.xlsx
@@ -413,14 +413,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F157"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="197" customWidth="1" min="3" max="3"/>
+    <col width="500" customWidth="1" min="3" max="3"/>
     <col width="83" customWidth="1" min="4" max="4"/>
-    <col width="83" customWidth="1" min="5" max="5"/>
+    <col width="75" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -458,100 +458,96 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A Qualitative Analysis of the German Road Traffic Regulations (StVO) for Automated Driving</t>
+          <t>3-digit occupation code images from the Norwegian census of 1950 - Manual review dataset</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sec M / Div 69 - Legal and accounting activities</t>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARTigo: Social Image Tagging (Aggregated Data)</t>
+          <t>Adaptive management and social-ecological recovery in Athabasca oil sands mine reclamation</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
-        </is>
-      </c>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARTigo: Social Image Tagging (Aggregated Data)</t>
+          <t>Dataset for "Scrabble yourself to success: Methods in teaching transcription."</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARTigo: Social Image Tagging (Aggregated Data)</t>
+          <t>GNSS Scintillation Data (60 s) at Bjørnøya in 2013</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -561,25 +557,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARTigo: Social Image Tagging (Raw Data)</t>
+          <t>GNSS Scintillation Data (60 s) at Bjørnøya in 2014</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -589,25 +585,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARTigo: Social Image Tagging (Raw Data)</t>
+          <t>GNSS Scintillation Data (60 s) at Bjørnøya in 2018</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -617,25 +613,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARTigo: Social Image Tagging (Raw Data)</t>
+          <t>GNSS Scintillation Data (60 s) at Bjørnøya in 2019</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -645,277 +641,305 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AfD Discourse Corpus (2013–2026): A Multi-Arena Corpus for Critical Discourse Analysis</t>
+          <t>GNSS Scintillation Data (60 s) at Bjørnøya in 2021</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sec F / Div 41 - Construction of buildings</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+        </is>
+      </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Banco de Dados QDA - CPI Covid-19</t>
+          <t>GNSS Scintillation Data (60 s) at Hopen in 2013</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+        </is>
+      </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>469</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CascadeMAP dataset of Design-of-Experiment optimization of glycerol detection pathway using fluorescence detection</t>
+          <t>GNSS Scintillation Data (60 s) at Hopen in 2014</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+        </is>
+      </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Data for the Manuscript with the Title: Structural and functional basis of antinociceptive action of χ-conotoxin AoIA at the noradrenaline transporter</t>
+          <t>GNSS Scintillation Data (60 s) at Hopen in 2015</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sec R / Div 93 - Sports activities and amusement and recreation activities</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+        </is>
+      </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dataset from: Healthcare professionals' experiences of encounters with family members exposed to violence perpetrated by patients with brain tumors: a qualitative study</t>
+          <t>GNSS Scintillation Data (60 s) at Hopen in 2017</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dataset from: Healthcare professionals' experiences of encounters with family members exposed to violence perpetrated by patients with brain tumors: a qualitative study</t>
+          <t>GNSS Scintillation Data (60 s) at Hopen in 2019</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dataset from: Healthcare professionals' experiences of encounters with family members exposed to violence perpetrated by patients with brain tumors: a qualitative study</t>
+          <t>GNSS Scintillation Data (60 s) at Hopen in 2020</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>927</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dataset to reproduce the figures of "Opposing entrainment effects of cloud droplet sedimentation during the pre-breakup stage of the stratocumulus to cumulus transition"</t>
+          <t>GNSS Scintillation Data (60 s) at Hopen in 2022</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+        </is>
+      </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Datasets for Tutorials on InSAR Time Series Analysis with SARvey and InSAR Explorer</t>
+          <t>GNSS Scintillation Data (60 s) at Hopen in 2023</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+        </is>
+      </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dynamic Surface Tension Database of Surfactants (DST‑SurfDB)</t>
+          <t>GNSS Scintillation Data (60 s) at Hopen in 2024</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+        </is>
+      </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Emergency design data</t>
+          <t>Informasjonsskriv</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -930,88 +954,96 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fast Breakdowns Observed in the Initial Leaders of Two Energetic Compact Strokes</t>
+          <t>Interviews about use of audience analytics and metrics and related news use</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
+        </is>
+      </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>From Failure to Persistence: A Lifecycle Study of Reliability in Stack Overflow Answers – Replication Package</t>
+          <t>Investigating rhoticity in Scottish Standard English with sociolinguistic interviews and corpus data: Auditory ratings</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sec J / Div 58 - Publishing activities</t>
+        </is>
+      </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>From Failure to Persistence: A Lifecycle Study of Reliability in Stack Overflow Answers – Replication Package</t>
+          <t>Manually annotated 3-digit occupation code training set from the Norwegian 1950 census</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Johnson Pandemic Corpus 2020 (JPanC20)</t>
+          <t>Manually annotated 3-digit occupation codes from the Norwegian 1950 census</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1019,51 +1051,51 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kuesioner Penelitian Pengaruh Bullying terhadap Kepercayaan Diri Siswa</t>
+          <t>Modernising sport psychology in football: Interview guides and supplementary data</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sec J / Div 63 - Information service activities</t>
+        </is>
+      </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oncodrive3D datasets</t>
+          <t>Questionnaire and interview data on passenger safety perception during autonomous ferry public trials</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1071,51 +1103,47 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Sec F / Div 41 - Construction of buildings</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plumbom et al. 2026</t>
+          <t>Replication Data for Effect of scalding temperature on sensory and biochemical properties in a hard goat milk cheese.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Proteomic and transcriptomic datasets of the desert cyanobacterium Gloeocapsopsis dulcis under long-term desiccation stress</t>
+          <t>Replication Data for: A Study of Refactorings During Software Change Tasks</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1125,25 +1153,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Qualitative Oral History Interview Transcripts on European Contemporary Dance Heritage</t>
+          <t>Replication Data for: A Three-Year Mixed Methods Study of Undergraduates’ Information Literacy Development: Knowing, Doing, and Feeling</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1153,25 +1181,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
+          <t>Sec R / Div 90 - Creative, arts and entertainment activities</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Qualitative Oral History Interview Transcripts on European Contemporary Dance Heritage</t>
+          <t>Replication Data for: A minute of your time: The impact  of survey recruitment method and  interview location on the value of  travel time</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1179,27 +1207,23 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Qualitative Oral History Interview Transcripts on European Contemporary Dance Heritage</t>
+          <t>Replication Data for: Cartobike transcripts focus group interviews</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1209,53 +1233,53 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
+          <t>Sec Q / Div 86 - Human health activities</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ToxKAN-Dataset</t>
+          <t>Replication Data for: På utsiden av mediedemokratiet. Et dypdykk i tankeprosessene hos mennesker med mistillit til nyheter, demokrati og digitalisering</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Transcriptional co-expression and sequence-model scoring of the Prochlorococcus MED4 CrY2H-seq interactome: a 227-run RNA-seq analysis with functional, WGCNA, and model-based cross-checks</t>
+          <t>Replication Data for: The effect of season, somatic cell count and bulk milk storage time on the sensory and chemical characteristics of an aged hard goat milk cheese</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1263,27 +1287,23 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Transcriptional co-expression and sequence-model scoring of the Prochlorococcus MED4 CrY2H-seq interactome: a 227-run RNA-seq analysis with functional, WGCNA, and model-based cross-checks</t>
+          <t>Replication data for: Potential Transcriptional Biomarkers to Guide Glucocorticoid Replacement in Autoimmune Addison’s Disease</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1293,105 +1313,101 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
+          <t>Sec Q / Div 86 - Human health activities</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UVIndoorLoc-BLE-AoA&amp;IQ Dataset</t>
+          <t>SENSE. interview needs and challenges of SENSE. target groups</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>QDA_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Implementation Science, Program Fidelity, and Program Delivery in Scaling Early Literacy Interventions for Children Aged 3–13: A Systematic Review</t>
+          <t>Search strategies for: Nursing leadership and management in home care: A qualitative scoping review</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec Q / Div 86 - Human health activities</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>QDA_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PLANET4B Business Models Dataset Pisa [UNIPI] 20251014 v2</t>
+          <t>Search strategies for: Nursing leadership and management in home care: A qualitative scoping review</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
+          <t>Sec Q / Div 86 - Human health activities</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>QDA_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PLANET4B Frame Analysis Dataset Pisa [UNIPI] 20251013 v2</t>
+          <t>Student interviews on learning strategies and digitalization</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1405,64 +1421,68 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>QDA_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Polish debates on higher education in the Sejm and party manifestos</t>
+          <t>Supplementary to: Stimulate, ventilate, collaborate –   A qualitative study underpinning the development of an educational guide to newborn resuscitation for midwifery students</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec Q / Div 86 - Human health activities</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>QDA_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Supporting Data for Scoping Review on Interlanguage Pragmatics in EFL Contexts</t>
+          <t>Supplementary to: Stimulate, ventilate, collaborate –   A qualitative study underpinning the development of an educational guide to newborn resuscitation for midwifery students</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Sec Q / Div 86 - Human health activities</t>
+        </is>
+      </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1471,26 +1491,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-04-08 Partial Solar Eclipse ESID#204</t>
+          <t>Supporting Data for: Differential expression of VA opsin transcript variants in tissues linked to photoperiodic time measurement in Svalbard rock ptarmigan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+          <t>Sec Q / Div 86 - Human health activities</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1499,26 +1519,26 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-04-08 Partial Solar Eclipse ESID#204</t>
+          <t>Supporting Data for: Institutionalizing International Internships in Business Education; An Action Research Approach to Overcoming Barriers and Driving Systemic Change in Norwegian Business Schools</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1527,26 +1547,26 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-04-08 Total Solar Eclipse ESID#292</t>
+          <t>Supporting Data for: Institutionalizing International Internships in Business Education; An Action Research Approach to Overcoming Barriers and Driving Systemic Change in Norwegian Business Schools</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1555,54 +1575,50 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04-08 Total Solar Eclipse ESID#294</t>
+          <t>Supporting data for "Welfare pens in dairy cattle herds with automatic milking systems – a descriptive study"</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+          <t>Sec Q / Div 88 - Social work activities without accommodation</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
+        <v>7</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>OTHER_PROJECT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Australian Election Study , 2007</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
         <v>1</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Aggregated thematic data and research materials: Anti-vegan focus groups in Greece and the Netherlands</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1611,7 +1627,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Aggregated thematic data and research materials: Anti-vegan focus groups in Greece and the Netherlands</t>
+          <t>Adaptation of migrants, 1979-1982: File 79a</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1621,16 +1637,16 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1639,7 +1655,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Aggregated thematic data and research materials: Anti-vegan focus groups in Greece and the Netherlands</t>
+          <t>Adaptation of migrants, 1979-1982: File 79b</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1649,16 +1665,16 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1667,22 +1683,26 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ant behaviour in the Anthropocene: A meta-analysis of human-induced environmental change effects on ant behaviour</t>
+          <t>Australian Election Study , 1996</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1691,22 +1711,26 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ant behaviour in the Anthropocene: A meta-analysis of human-induced environmental change effects on ant behaviour</t>
+          <t>Australian Election Study , 2010</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1715,7 +1739,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Asynchrony of ageing among traits in a wild bird population</t>
+          <t>Australian Election Study , 2013</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1723,14 +1747,18 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
       <c r="F49" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1739,22 +1767,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bridging Sensory Science and Economic Value</t>
+          <t>Australian Election Study , 2016</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1763,26 +1795,26 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CARDIOMED Registry — Anonymised Dataset: Haematocrit and in-hospital mortality in ADHF at 2,600 m a.s.l.</t>
+          <t>Australian Election Study , 2019</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1791,308 +1823,284 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CARDIOMED Registry — Anonymised Dataset: Haematocrit and in-hospital mortality in ADHF at 2,600 m a.s.l.</t>
+          <t>Australian Election Study Online, 2001</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>QD_PROJECT</t>
+          <t>OTHER_PROJECT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DEVELOPING LINGUODISCURSIVE COMPETENCE IN THE DIGITAL TOURISM ENVIRONMENT: LINGUOPRAGMATIC FEATURES OF ONLINE PLATFORMS AND MULTIMODAL COMMUNICATION</t>
+          <t>A hand-list of the Muḥammadan manuscripts, including all those written in the arabic character, preserved in the library of the university of Cambridge</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+          <t>Sec R / Div 91 - Libraries, archives, museums and other cultural activities</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>QD_PROJECT</t>
+          <t>OTHER_PROJECT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DEVELOPING LINGUODISCURSIVE COMPETENCE IN THE DIGITAL TOURISM ENVIRONMENT: LINGUOPRAGMATIC FEATURES OF ONLINE PLATFORMS AND MULTIMODAL COMMUNICATION</t>
+          <t>Annus Novus Et Sanctus, Sive Praxis Exercitiorum Spiritualium S. P. Ignatii : Usu Annuo Primùm post Annum sanctum, utiliter &amp; sanctè frequentanda ; Xenium Almæ Congretationi Majori Sub Titulo, &amp; Præsidio B. V. Mariæ Ab Angelo Salutatæ Fuldæ oblatum, Anno M.DCC.XXVI. Cum permissu Superiorum</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>QD_PROJECT</t>
+          <t>OTHER_PROJECT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DIGITAL TRANSFORMATION AND AI-DRIVEN SUPPLY CHAIN IMPROVEMENT IN THE INDONESIAN AGROCHEMICAL INDUSTRY</t>
+          <t>Changing educational aspirations of children living in poverty in Ethiopia / Yisak Tafere</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Sec M / Div 69 - Legal and accounting activities</t>
-        </is>
-      </c>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>QD_PROJECT</t>
+          <t>OTHER_PROJECT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DIGITAL TRANSFORMATION AND AI-DRIVEN SUPPLY CHAIN IMPROVEMENT IN THE INDONESIAN AGROCHEMICAL INDUSTRY</t>
+          <t>Chronic poverty in rural Ethiopia through the lens of life histories / Laura Camfield and Keetie Roelen</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Sec M / Div 69 - Legal and accounting activities</t>
-        </is>
-      </c>
+          <t>Sec A / Div 01 - Crop and animal production, hunting and related service activities</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>QD_PROJECT</t>
+          <t>OTHER_PROJECT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DIGITAL TRANSFORMATION AND AI-DRIVEN SUPPLY CHAIN IMPROVEMENT IN THE INDONESIAN AGROCHEMICAL INDUSTRY</t>
+          <t>Courier du Bas-Rhin</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Sec M / Div 69 - Legal and accounting activities</t>
-        </is>
-      </c>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>QD_PROJECT</t>
+          <t>OTHER_PROJECT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Data and Scripts for: Techno-Economic Analysis of Hydrocarbon-CO2 Binary Mixtures in Heat Pump-Based Thermal Energy Storages</t>
+          <t>Der neu-aramaeische Dialekt des Ṭûr ʿAbdîn : syrische Sagen und Märchen aus dem Volksmunde</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
-        </is>
-      </c>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>QD_PROJECT</t>
+          <t>OTHER_PROJECT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Data and Scripts for: Techno-Economic Analysis of Hydrocarbon-CO2 Binary Mixtures in Heat Pump-Based Thermal Energy Storages</t>
+          <t>Established and Outsiders at the Same Time - Self-Images and We-Images of Palestinians in the West Bank and in Israel</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
           <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>QD_PROJECT</t>
+          <t>OTHER_PROJECT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Data for "Predominant proton insertion during electrochemical cycling of ε-VOPO4 in a non-aqueous Ca ion electrolyte"</t>
+          <t>Grammaire Turque Ou Développement Séparé Et Méthodique Des Trois Genres De Style Usités, Savoir L'Arabe, Le Persan Et Le Tartare / Par Auguste Pfizmaier, Docteur En Médecine Et Professeur Public Extraordinaire De Langues Orientales À L'Université De Vienne</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>QD_PROJECT</t>
+          <t>OTHER_PROJECT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Data for: "The limited communication of corrections to users of scholarly platforms"</t>
+          <t>Iac. Frid. Ludovici, Icti. Vsvs Practicvs Distinctionvm Ivridicarvm : Ivxta Seriem Digestorum Adornatus / Recensitus, Illustratvs In Articvlis Ivris Saxonici Ad Ordinat. Process. Electoral. Saxon. Recognitam Adcommodatvs, Novis Distinictionibvs Ac Qvamplvrimis Practicis Observantionibvs Locvpletatuvs A Io. Gerardo Schlittio; Icto, Potentiss. Regi Borvss. A Consil. Avl. Et prof. Ivr. Ordinar. In Regia Fridericiana ...</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>QD_PROJECT</t>
+          <t>OTHER_PROJECT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Data from: Fitness change in relation to mutation number in spontaneous mutation accumulation lines of Chlamydomonas reinhardtii</t>
+          <t>Imp. Caes. Augusti Temporum Notatio, Genus, Et Scriptorum Fragmenta. Praemittitur Nicolai Damasceni Liber De Institutione Augusti Cum Versione Hug. Grotii et Henr. Valesii Notis / Curante Jo. Alberto Fabricio, D. &amp; Prof. Publico in Gymnasio Hamburgensi</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>QD_PROJECT</t>
+          <t>OTHER_PROJECT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Data set Non-volatile metabolite profiling integrated with QDA sensory evaluation of white tea</t>
+          <t>Institutionum Physicae ... Conscripta In Usum Tironum Philosophiae</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2102,143 +2110,127 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>QD_PROJECT</t>
+          <t>OTHER_PROJECT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Data, analysis codes, analysis output and survey questionnaire for: Integrating Threatened Biodiversity in Monetary Ecosystem Accounting: Choice Experiments and Simulated Exchange Values</t>
+          <t>Praktische Grammatik der osmanisch-türkischen Sprache / von Adolf Wahrmund</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Sec J / Div 63 - Information service activities</t>
-        </is>
-      </c>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>QD_PROJECT</t>
+          <t>OTHER_PROJECT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Data, analysis codes, analysis output and survey questionnaire for: Integrating Threatened Biodiversity in Monetary Ecosystem Accounting: Choice Experiments and Simulated Exchange Values</t>
+          <t>Ruling Palestine / International Crisis Group</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Sec J / Div 63 - Information service activities</t>
-        </is>
-      </c>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>QD_PROJECT</t>
+          <t>OTHER_PROJECT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dataset for Realization of QDA</t>
+          <t>T. Livii Patavini Historiarvm Libri Qvi Svpersvnt Omnes</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sec R / Div 90 - Creative, arts and entertainment activities</t>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>QD_PROJECT</t>
+          <t>OTHER_PROJECT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dataset for Teleconnection-Based Modeling of Extreme Precipitation in South America Using Climate Indices</t>
+          <t>Wohlgegründete Anmerckungen Auf die Jn Druck gegebene Allerunterthänigste Fernere Anzeige und Exceptiones Nullitatis, itemque sub- &amp; obreptionis Anwalds Sr. Chur- Fürstl. Durchl. zu Brandenburg contra Die Fr. Abbatiszin zu Quedlinburg Durchl. pro Cassatione Mandati inhibitorii, Cassatorii &amp; restitutorii S. C. pœnalis, mit Beylagen von N.1. biß 75. Anno MDCC. Auf gnädigsten Befehl Hochbesagter Frauen Abbatißin zu Quedlinburg Durchl. zu Pappier gebracht und mit Beylagen á Nro. I. biß LXXVI. bestär</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>QD_PROJECT</t>
+          <t>OTHER_PROJECT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dataset for Teleconnection-Based Modeling of Extreme Precipitation in South America Using Climate Indices</t>
+          <t>Élémens De La Langue Turque, Ou Tables Analytiques De La Langue Turque Usuelle, Avec Leur Développement / ... Sous les auspices de M. Le Comte De Choiseul-Gouffier, Ambassadeur de Sa Mejesté Très-Chrétienne près la Porte Ottomane, Par M. Viguier, Préfet Apostolique des Établissemens de la Congrégation de la Mission dans le Levant</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
+          <t>Sec N / Div 82 - Office administrative, office support and other business support</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2247,26 +2239,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dataset: Chicago Atlantic Real Estate Finance, Inc. (REFI) Stock Performance</t>
+          <t>"I had no choice!" : Challenges in the informed consent and decision-making process for allogeneic stem cell transplantation : a qualitative method triangulation</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Sec R / Div 90 - Creative, arts and entertainment activities</t>
-        </is>
-      </c>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2275,22 +2263,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Datensatz der Expert:inneninterviews im Projekt RPSKM / Dataset of the expert interviews in the project RPCSA</t>
+          <t>"If I don't smoke shisha, I won't be able to sleep" : lived experiences of high school students in Ethiopia</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2299,26 +2287,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ecological Political Economy: a critical realist approach to ecological economics and political ecology</t>
+          <t>'I am no longer anxious when I speak' : experiences of people with primary progressive aphasia taking part in a biographic-narrative therapy (Cope PPA)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
-        </is>
-      </c>
+          <t>Sec Q / Div 86 - Human health activities</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2327,26 +2311,26 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ecological Political Economy: a critical realist approach to ecological economics and political ecology</t>
+          <t>A Mixed-Methods Study on Google Classroom Use: Thematic Perspectives and Quantitative Insights on Student Engagement and Connectivity at the City of Malabon University</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
+          <t>Sec P / Div 85 - Education</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2355,26 +2339,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ecological Political Economy: a critical realist approach to ecological economics and political ecology</t>
+          <t>A model-based cortical parcellation scheme for high-resolution 7 Tesla MRI data</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Sec K / Div 64 - Financial service activities, except insurance and pension funding</t>
-        </is>
-      </c>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2383,22 +2363,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Efficient globin production during terminal erythropoiesis depends on the cooperative action of TENT5C poly(A) polymerase and LARP4B</t>
+          <t>A semi-automated HTTP traffic analysis for online payments for empowering security, forensics and privacy analysis</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2407,22 +2387,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Efficient globin production during terminal erythropoiesis depends on the cooperative action of TENT5C poly(A) polymerase and LARP4B</t>
+          <t>Applying qualitative comparative analysis in a systematic review : lessons learned</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2431,7 +2411,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Explore Wales: A Geospatial Dataset of Heritage and Visitor Locations</t>
+          <t>Availability and utilization of psychosocial services for breast cancer patients in Addis Ababa, Ethiopia : a mixed method study</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2441,7 +2421,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec Q / Div 86 - Human health activities</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2450,7 +2430,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2459,7 +2439,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Extracted Data from a Scoping Review of Machine Learning Approaches for Wave Propagation Modeling in Seismology</t>
+          <t>Barriers to adherence to cervical cancer screening care in Northern Tanzania</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2467,18 +2447,14 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -2487,7 +2463,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Extracted Data from a Scoping Review of Machine Learning Approaches for Wave Propagation Modeling in Seismology</t>
+          <t>Belastungen und Beanspruchungen von Angehörigen von Patienten mit ARDS auf Intensivstation : Eine qualitative Interviewstudie anhand eines Belastungs-Beanspruchungs-Modells</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2497,16 +2473,16 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sec P / Div 85 - Education</t>
+          <t>Sec Q / Div 86 - Human health activities</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -2515,7 +2491,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Extracted Data from a Scoping Review of Machine Learning Approaches for Wave Propagation Modeling in Seismology</t>
+          <t>Challenges of initial TVET teacher training in Indonesia : empirical analysis of skills deficit of mechanical engineering teachers</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2523,18 +2499,14 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -2543,22 +2515,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FORGE code, trained models and source data for RNA tertiary-structure information mapping</t>
+          <t>Competitive Human Capital as a Key Factor in the Development of Green Energy in Central Asia</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -2567,22 +2539,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FORGE code, trained models and source data for RNA tertiary-structure information mapping</t>
+          <t>Conception of a barrier-free mobile social network app for people with intellectual disabilities</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -2591,7 +2563,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Genomic, CRISPR, and structural datasets underlying Vibrio–phage interaction and defense system analysis</t>
+          <t>Content validity of the EORTC quality of life questionnaire QLQ-C30 for use in cancer</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2601,12 +2573,12 @@
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -2615,26 +2587,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>High-resolution Multi-environmental-indicator Livestock Emissions of China (HMLE-China): A 1-km Stage-resolved Emission Inventory</t>
+          <t>DASC-PM v1.1 A Process Model for Data Science Projects</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sec M / Div 69 - Legal and accounting activities</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
+          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -2643,7 +2611,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Improved Iso-Seq-based genome annotations for Australian wild rice species O. rufipogon and O. meridionalis</t>
+          <t>Enhancing transsectoral interdisciplinary patient-centered care for patients with rare cancers : protocol for a mixed methods process evaluation</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2651,14 +2619,18 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Sec Q / Div 86 - Human health activities</t>
+        </is>
+      </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -2667,7 +2639,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Influence of Structural Disorder on Self-Trapped Exciton Luminescence in Natural Quartz</t>
+          <t>Experienced teachers talking about their mathematics teaching with linguistically disadvantaged learners</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2675,14 +2647,18 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
       <c r="F85" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -2691,26 +2667,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Investigating Enablers, Barriers, and Consequences of Psychological Safety in Software Engineering</t>
+          <t>Factors contributing to late breast cancer diagnosis : a qualitative study on the patient’s perspective in Tanzania</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
           <t>Sec Q / Div 86 - Human health activities</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -2719,7 +2691,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Master Analytical Dataset: ESP-Content Collaborative Teaching and Longitudinal Student Motivation Frameworks (Vols. 1–7)</t>
+          <t>German physicians’ perceptions and views on complementary medicine in pediatric oncology : a qualitative study</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2727,18 +2699,14 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -2747,7 +2715,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Master Analytical Dataset: ESP-Content Collaborative Teaching and Longitudinal Student Motivation Frameworks (Vols. 1–7)</t>
+          <t>Harmonizing rigor, relevance, and insight : a mixed inductive approach for qualitative analysis with the Gioia methodology and the GABEK® method</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2755,18 +2723,14 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -2775,26 +2739,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Master Analytical Dataset: ESP-Content Collaborative Teaching and Longitudinal Student Motivation Frameworks (Vols. 1–7)</t>
+          <t>Health system challenges in the diagnostic and treatment pathway for patients with suspected cervical cancer : a qualitative study</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
+          <t>Sec Q / Div 86 - Human health activities</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -2803,22 +2763,26 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Model and code for: Assessing the Cost of CO₂ Avoided for CCS in the Cement Industry: A Comparative Analysis of Denmark and Germany</t>
+          <t>Hospital discharge planning in cardiac care : study protocol for a mixed-methods study on the implementation, influencing factors and quality of care in Germany</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Sec Q / Div 86 - Human health activities</t>
+        </is>
+      </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -2827,22 +2791,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Model and code for: Assessing the Cost of CO₂ Avoided for CCS in the Cement Industry: A Comparative Analysis of Denmark and Germany</t>
+          <t>Identifying similarities of big data projects : a use case driven approach</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -2851,26 +2815,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Music Therapy Today (World Federation of Music Therapy): a bibliometric and content-analysis dataset, 2000–2023</t>
+          <t>Implementing ethical aspects in the development of a robotic system for nursing care : a qualitative approach</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
           <t>Sec Q / Div 86 - Human health activities</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -2879,7 +2839,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Open Science Monitoring Initiatives Dataset v01</t>
+          <t>Integrative analysis of metabolic models : from structure to dynamics</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2887,18 +2847,14 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -2907,26 +2863,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Open Science Monitoring Initiatives Dataset v01</t>
+          <t>Introducing DASC-PM: A Data Science Process Model</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
           <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -2935,26 +2887,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Open Science Monitoring Initiatives Dataset v01</t>
+          <t>Local colonisations and extinctions of European birds are poorly explained by changes in climate suitability</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
+          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -2963,7 +2911,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Physiological adaption of Fusarium commune to oxygen limitation under denitrifying conditions is primarily linked to energy conservation by substrate level phosphorylation</t>
+          <t>Mathematical and Statistical Methods of Analyzing the Successful Implementation of German-Ukrainian Projects</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2973,12 +2921,12 @@
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -2987,26 +2935,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Process of Process Mining: A Multi-perspective Event Log</t>
+          <t>Multidimensional Model of Sebastian Unger’s Idiostyle in Poetic Creativity: Corpus Analysis and NLP Methods</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
-        </is>
-      </c>
+          <t>Sec M / Div 72 - Scientific research and development</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -3015,26 +2959,26 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Process of Process Mining: A Multi-perspective Event Log</t>
+          <t>Perspectives of policy and political decision makers on access to formal dementia care : expert interviews in eight European countries</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Sec J / Div 63 - Information service activities</t>
+          <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
+          <t>Sec M / Div 69 - Legal and accounting activities</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -3043,7 +2987,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Research Dataset: Schutzian Phenomenological Analysis of Civic Identity Formation in Pesantren Families, West Java</t>
+          <t>Primary nursing in the intensive care unit : a qualitative analysis of an implementation process</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3051,14 +2995,18 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Sec Q / Div 86 - Human health activities</t>
+        </is>
+      </c>
       <c r="F99" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -3067,7 +3015,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Research Dataset: Schutzian Phenomenological Analysis of Civic Identity Formation in Pesantren Families, West Java</t>
+          <t>Private households in Central Asia: methodological reflections on an empirical research (2012-2014)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3077,12 +3025,12 @@
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -3091,7 +3039,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Research Dataset: Schutzian Phenomenological Analysis of Civic Identity Formation in Pesantren Families, West Java</t>
+          <t>Stakeholder governance to facilitate collaboration for a systemic circular economy transition : a qualitative study in the European chemicals and plastics industry</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3101,12 +3049,12 @@
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -3115,26 +3063,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Supplementary Info Package - Developer Task Delegation to LLMs and the Trust Factor: A Mixed Methods Study</t>
+          <t>Supporting science pre-service elementary teachers in learning to plan modeling-based investigations</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
+          <t>Sec P / Div 85 - Education</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -3143,7 +3087,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Supplementary Info Package - Developer Task Delegation to LLMs and the Trust Factor: A Mixed Methods Study</t>
+          <t>The decision-making process for sedation in specialist palliative care : a qualitative interview study with team members, relatives, and patients</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3153,16 +3097,16 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
+          <t>Sec Q / Div 86 - Human health activities</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -3171,26 +3115,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Supplementary Info Package - Developer Task Delegation to LLMs and the Trust Factor: A Mixed Methods Study</t>
+          <t>The perspectives of healthcare providers, traditional healers, and other key informants on the late diagnosis of breast cancer in northern Tanzania : a qualitative study</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
+          <t>Sec Q / Div 86 - Human health activities</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -3199,7 +3139,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Supplymentary Materials for "Who Pays the Review Cost? Triage, Fairness, and Accountability in AI-authored Pull Requests"</t>
+          <t>fMRI investigations of visual cortex dynamics : impact of peripheral visual field restrictions</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3207,18 +3147,14 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -3227,7 +3163,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Supplymentary Materials for "Who Pays the Review Cost? Triage, Fairness, and Accountability in AI-authored Pull Requests"</t>
+          <t>‘As long as I have a restroom somewhere […], I am fine’ : a qualitative study on the perspectives of peri- and postmenopausal women on the impact of the urinary component of the genitourinary syndrome of menopause (GSM)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3235,18 +3171,14 @@
           <t>Sec M / Div 72 - Scientific research and development</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -3255,22 +3187,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>THE ROLE OF THE JOURNEY MOTIF IN THE EVOLUTION OF LITERARY HEROES: A COMPARATIVE STUDY OF ENGLISH AND UZBEK LITERATURE</t>
+          <t>“DLQI Seems to be ‘Action’, and Skindex-29 Seems to be ‘Emotion’” : qualitative study of the perceptions of patients with psoriasis or eczema on two common dermatology-specific quality of life measures</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
+          <t>Sec Q / Div 86 - Human health activities</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -3279,7 +3211,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>THE ROLE OF THE JOURNEY MOTIF IN THE EVOLUTION OF LITERARY HEROES: A COMPARATIVE STUDY OF ENGLISH AND UZBEK LITERATURE</t>
+          <t>“How can a woman live without having a breast?” : challenges related to mastectomy in Ethiopia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3289,1311 +3221,7 @@
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>1</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>THE ROLE OF THE JOURNEY MOTIF IN THE EVOLUTION OF LITERARY HEROES: A COMPARATIVE STUDY OF ENGLISH AND UZBEK LITERATURE</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>1</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Table S1. Frequency table derived from the inductive qualitative analysis.</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>1</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Table S1. Frequency table derived from the inductive qualitative analysis.</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>1</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Technischer Vergleich von CAQDAS Funktionalitäten in 2026</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>1</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Thermographic data for manuscript Mus.4189-D-14,8 (SLUB)</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>1</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Thermographic data for manuscript Mus.4645-D-1 (SLUB)</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>1</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Thermographic data for manuscript Mus.4657-D-503 (SLUB)</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>6</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>3-digit occupation code images from the Norwegian census of 1950 - Manual review dataset</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>6</v>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Adaptive management and social-ecological recovery in Athabasca oil sands mine reclamation</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>6</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Dataset for "Scrabble yourself to success: Methods in teaching transcription."</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>6</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>GNSS Scintillation Data (60 s) at Bjørnøya in 2013</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>6</v>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>GNSS Scintillation Data (60 s) at Bjørnøya in 2014</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>6</v>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>GNSS Scintillation Data (60 s) at Bjørnøya in 2018</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>6</v>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>GNSS Scintillation Data (60 s) at Bjørnøya in 2019</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>6</v>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>GNSS Scintillation Data (60 s) at Bjørnøya in 2021</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>6</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>GNSS Scintillation Data (60 s) at Hopen in 2013</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
-      <c r="F124" t="n">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>6</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>GNSS Scintillation Data (60 s) at Hopen in 2014</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>6</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>GNSS Scintillation Data (60 s) at Hopen in 2015</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>6</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>GNSS Scintillation Data (60 s) at Hopen in 2017</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>6</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>GNSS Scintillation Data (60 s) at Hopen in 2019</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
-      <c r="F128" t="n">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>6</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>GNSS Scintillation Data (60 s) at Hopen in 2020</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>6</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>GNSS Scintillation Data (60 s) at Hopen in 2022</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
-      <c r="F130" t="n">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>6</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>GNSS Scintillation Data (60 s) at Hopen in 2023</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
-      <c r="F131" t="n">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>6</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>GNSS Scintillation Data (60 s) at Hopen in 2024</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Sec E / Div 38 - Waste collection, treatment and disposal activities</t>
-        </is>
-      </c>
-      <c r="F132" t="n">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>6</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Informasjonsskriv</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>6</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Interviews about use of audience analytics and metrics and related news use</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Sec J / Div 59 - Motion picture, video and television programme production</t>
-        </is>
-      </c>
-      <c r="F134" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>6</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Investigating rhoticity in Scottish Standard English with sociolinguistic interviews and corpus data: Auditory ratings</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Sec J / Div 58 - Publishing activities</t>
-        </is>
-      </c>
-      <c r="F135" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>6</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Manually annotated 3-digit occupation code training set from the Norwegian 1950 census</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>6</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Manually annotated 3-digit occupation codes from the Norwegian 1950 census</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>6</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Modernising sport psychology in football: Interview guides and supplementary data</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Sec J / Div 63 - Information service activities</t>
-        </is>
-      </c>
-      <c r="F138" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>6</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Questionnaire and interview data on passenger safety perception during autonomous ferry public trials</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>6</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Replication Data for Effect of scalding temperature on sensory and biochemical properties in a hard goat milk cheese.</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>6</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Replication Data for: A Study of Refactorings During Software Change Tasks</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Sec J / Div 62 - Computer programming, consultancy and related activities</t>
-        </is>
-      </c>
-      <c r="F141" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>6</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Replication Data for: A Three-Year Mixed Methods Study of Undergraduates’ Information Literacy Development: Knowing, Doing, and Feeling</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Sec R / Div 90 - Creative, arts and entertainment activities</t>
-        </is>
-      </c>
-      <c r="F142" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>6</v>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Replication Data for: A minute of your time: The impact  of survey recruitment method and  interview location on the value of  travel time</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>6</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Replication Data for: Cartobike transcripts focus group interviews</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
-        </is>
-      </c>
-      <c r="F144" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>6</v>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Replication Data for: På utsiden av mediedemokratiet. Et dypdykk i tankeprosessene hos mennesker med mistillit til nyheter, demokrati og digitalisering</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="F145" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>6</v>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Replication Data for: The effect of season, somatic cell count and bulk milk storage time on the sensory and chemical characteristics of an aged hard goat milk cheese</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>6</v>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Replication data for: Potential Transcriptional Biomarkers to Guide Glucocorticoid Replacement in Autoimmune Addison’s Disease</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
-        </is>
-      </c>
-      <c r="F147" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>6</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>SENSE. interview needs and challenges of SENSE. target groups</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="F148" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>6</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Search strategies for: Nursing leadership and management in home care: A qualitative scoping review</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>6</v>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Search strategies for: Nursing leadership and management in home care: A qualitative scoping review</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>6</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Student interviews on learning strategies and digitalization</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="F151" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>6</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Supplementary to: Stimulate, ventilate, collaborate –   A qualitative study underpinning the development of an educational guide to newborn resuscitation for midwifery students</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
-        </is>
-      </c>
-      <c r="F152" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>6</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Supplementary to: Stimulate, ventilate, collaborate –   A qualitative study underpinning the development of an educational guide to newborn resuscitation for midwifery students</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
-        </is>
-      </c>
-      <c r="F153" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>6</v>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Supporting Data for: Differential expression of VA opsin transcript variants in tissues linked to photoperiodic time measurement in Svalbard rock ptarmigan</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Sec Q / Div 86 - Human health activities</t>
-        </is>
-      </c>
-      <c r="F154" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>6</v>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Supporting Data for: Institutionalizing International Internships in Business Education; An Action Research Approach to Overcoming Barriers and Driving Systemic Change in Norwegian Business Schools</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="F155" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>6</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Supporting Data for: Institutionalizing International Internships in Business Education; An Action Research Approach to Overcoming Barriers and Driving Systemic Change in Norwegian Business Schools</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Sec P / Div 85 - Education</t>
-        </is>
-      </c>
-      <c r="F156" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>6</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>QD_PROJECT</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Supporting data for "Welfare pens in dairy cattle herds with automatic milking systems – a descriptive study"</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Sec M / Div 72 - Scientific research and development</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Sec Q / Div 88 - Social work activities without accommodation</t>
-        </is>
-      </c>
-      <c r="F157" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
